--- a/GearSage-client/pkgGear/data_raw/shimano_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_lure_import.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:N66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -441,13 +441,16 @@
       <c r="M1" t="str">
         <v>updated_at</v>
       </c>
+      <c r="N1" t="str">
+        <v>description</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>SL1000</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
         <v>Bantam ARMAJOINT 190SF FLASH BOOST</v>
@@ -480,6 +483,9 @@
         <v/>
       </c>
       <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
         <v/>
       </c>
     </row>
@@ -487,8 +493,8 @@
       <c r="A3" t="str">
         <v>SL1001</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v>FACER 85+SF</v>
@@ -521,6 +527,9 @@
         <v/>
       </c>
       <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
         <v/>
       </c>
     </row>
@@ -528,8 +537,8 @@
       <c r="A4" t="str">
         <v>SL1002</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>MD ZUMVERNO 95SP</v>
@@ -562,6 +571,9 @@
         <v/>
       </c>
       <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v/>
       </c>
     </row>
@@ -569,8 +581,8 @@
       <c r="A5" t="str">
         <v>SL1003</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v>LIGEN 66F WALKING SPEC</v>
@@ -603,6 +615,9 @@
         <v/>
       </c>
       <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
         <v/>
       </c>
     </row>
@@ -610,8 +625,8 @@
       <c r="A6" t="str">
         <v>SL1004</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v>Bantam ARMAJOINT 280SF ARMABOOST</v>
@@ -644,6 +659,9 @@
         <v/>
       </c>
       <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
         <v/>
       </c>
     </row>
@@ -651,8 +669,8 @@
       <c r="A7" t="str">
         <v>SL1005</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>GRAVITATOR 220SF ARMABOOST/FLASH BOOST</v>
@@ -685,6 +703,9 @@
         <v/>
       </c>
       <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <v/>
       </c>
     </row>
@@ -692,8 +713,8 @@
       <c r="A8" t="str">
         <v>SL1006</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="str">
         <v>Bantam ARMAJOINT 190F FLASH BOOST</v>
@@ -726,6 +747,9 @@
         <v/>
       </c>
       <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v/>
       </c>
     </row>
@@ -733,8 +757,8 @@
       <c r="A9" t="str">
         <v>SL1007</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
+      <c r="B9">
+        <v>1</v>
       </c>
       <c r="C9" t="str">
         <v>Bantam BT BAIT 77F</v>
@@ -767,6 +791,9 @@
         <v/>
       </c>
       <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <v/>
       </c>
     </row>
@@ -774,8 +801,8 @@
       <c r="A10" t="str">
         <v>SL1008</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
+      <c r="B10">
+        <v>1</v>
       </c>
       <c r="C10" t="str">
         <v>Bantam BT BAIT 99SS</v>
@@ -808,6 +835,9 @@
         <v/>
       </c>
       <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v/>
       </c>
     </row>
@@ -815,8 +845,8 @@
       <c r="A11" t="str">
         <v>SL1009</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>SCORPION WORLD JERK 110F/110S FLASH BOOST</v>
@@ -849,6 +879,9 @@
         <v/>
       </c>
       <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
         <v/>
       </c>
     </row>
@@ -856,8 +889,8 @@
       <c r="A12" t="str">
         <v>SL1010</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>1</v>
       </c>
       <c r="C12" t="str">
         <v>SCORPION WORLD JERK 115F/115S FLASH BOOST</v>
@@ -890,6 +923,9 @@
         <v/>
       </c>
       <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
         <v/>
       </c>
     </row>
@@ -897,8 +933,8 @@
       <c r="A13" t="str">
         <v>SL1011</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>1</v>
       </c>
       <c r="C13" t="str">
         <v>Bantam WORLD MINNOW 115SP FLASH BOOST</v>
@@ -931,6 +967,9 @@
         <v/>
       </c>
       <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <v/>
       </c>
     </row>
@@ -938,8 +977,8 @@
       <c r="A14" t="str">
         <v>SL1012</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>1</v>
       </c>
       <c r="C14" t="str">
         <v>Bantam WORLD MINNOW 115F FLASH BOOST</v>
@@ -972,6 +1011,9 @@
         <v/>
       </c>
       <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
         <v/>
       </c>
     </row>
@@ -979,8 +1021,8 @@
       <c r="A15" t="str">
         <v>SL1013</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15" t="str">
         <v>Bantam WORLD CRANK 73F FLASH BOOST</v>
@@ -1013,6 +1055,9 @@
         <v/>
       </c>
       <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <v/>
       </c>
     </row>
@@ -1020,8 +1065,8 @@
       <c r="A16" t="str">
         <v>SL1014</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>1</v>
       </c>
       <c r="C16" t="str">
         <v>Bantam ZUMVERNO 95SP FLASH BOOST</v>
@@ -1054,6 +1099,9 @@
         <v/>
       </c>
       <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
         <v/>
       </c>
     </row>
@@ -1061,8 +1109,8 @@
       <c r="A17" t="str">
         <v>SL1015</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>1</v>
       </c>
       <c r="C17" t="str">
         <v>Bantam WORLD POP 69F FLASH BOOST</v>
@@ -1095,6 +1143,9 @@
         <v/>
       </c>
       <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <v/>
       </c>
     </row>
@@ -1102,8 +1153,8 @@
       <c r="A18" t="str">
         <v>SL1016</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18" t="str">
         <v>SCORPION JERK 90S JET BOOST</v>
@@ -1136,6 +1187,9 @@
         <v/>
       </c>
       <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
         <v/>
       </c>
     </row>
@@ -1143,8 +1197,8 @@
       <c r="A19" t="str">
         <v>SL1017</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>1</v>
       </c>
       <c r="C19" t="str">
         <v>Bantam WORLD RUSH 56F FLASH BOOST</v>
@@ -1177,6 +1231,9 @@
         <v/>
       </c>
       <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <v/>
       </c>
     </row>
@@ -1184,8 +1241,8 @@
       <c r="A20" t="str">
         <v>SL1018</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="str">
         <v>Bantam UNDURATOR 88F FLASH BOOST</v>
@@ -1218,6 +1275,9 @@
         <v/>
       </c>
       <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
         <v/>
       </c>
     </row>
@@ -1225,8 +1285,8 @@
       <c r="A21" t="str">
         <v>SL1019</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>Bantam OLIVA CRANK FLAT 65F FLASH BOOST</v>
@@ -1259,6 +1319,9 @@
         <v/>
       </c>
       <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
         <v/>
       </c>
     </row>
@@ -1266,8 +1329,8 @@
       <c r="A22" t="str">
         <v>SL1020</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="B22">
+        <v>1</v>
       </c>
       <c r="C22" t="str">
         <v>Bantam ENBER 60SP FLASH BOOST</v>
@@ -1300,6 +1363,9 @@
         <v/>
       </c>
       <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
         <v/>
       </c>
     </row>
@@ -1307,8 +1373,8 @@
       <c r="A23" t="str">
         <v>SL1021</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>1</v>
       </c>
       <c r="C23" t="str">
         <v>Bantam LIGEN 66F FLASH BOOST</v>
@@ -1341,6 +1407,9 @@
         <v/>
       </c>
       <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
         <v/>
       </c>
     </row>
@@ -1348,8 +1417,8 @@
       <c r="A24" t="str">
         <v>SL1022</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="B24">
+        <v>1</v>
       </c>
       <c r="C24" t="str">
         <v>Bantam MD ZUMVERNO 115SP/115SP FLASH BOOST</v>
@@ -1382,6 +1451,9 @@
         <v/>
       </c>
       <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
         <v/>
       </c>
     </row>
@@ -1389,8 +1461,8 @@
       <c r="A25" t="str">
         <v>SL1023</v>
       </c>
-      <c r="B25" t="str">
-        <v/>
+      <c r="B25">
+        <v>1</v>
       </c>
       <c r="C25" t="str">
         <v>Bantam SWAGY MDW</v>
@@ -1423,6 +1495,9 @@
         <v/>
       </c>
       <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
         <v/>
       </c>
     </row>
@@ -1430,8 +1505,8 @@
       <c r="A26" t="str">
         <v>SL1024</v>
       </c>
-      <c r="B26" t="str">
-        <v/>
+      <c r="B26">
+        <v>1</v>
       </c>
       <c r="C26" t="str">
         <v>Bantam SWAGY TW/DW</v>
@@ -1464,6 +1539,9 @@
         <v/>
       </c>
       <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <v/>
       </c>
     </row>
@@ -1471,8 +1549,8 @@
       <c r="A27" t="str">
         <v>SL1025</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>1</v>
       </c>
       <c r="C27" t="str">
         <v>Bantam JIJIL 70</v>
@@ -1505,6 +1583,9 @@
         <v/>
       </c>
       <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
         <v/>
       </c>
     </row>
@@ -1512,8 +1593,8 @@
       <c r="A28" t="str">
         <v>SL1026</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
+      <c r="B28">
+        <v>1</v>
       </c>
       <c r="C28" t="str">
         <v>Bantam MACBETH 50 RATTLE</v>
@@ -1546,6 +1627,9 @@
         <v/>
       </c>
       <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
         <v/>
       </c>
     </row>
@@ -1553,8 +1637,8 @@
       <c r="A29" t="str">
         <v>SL1027</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
+      <c r="B29">
+        <v>1</v>
       </c>
       <c r="C29" t="str">
         <v>Bantam JIJIL PROP 67SS</v>
@@ -1587,6 +1671,9 @@
         <v/>
       </c>
       <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
         <v/>
       </c>
     </row>
@@ -1594,8 +1681,8 @@
       <c r="A30" t="str">
         <v>SL1028</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
+      <c r="B30">
+        <v>1</v>
       </c>
       <c r="C30" t="str">
         <v>Bantam MACBETH SHALLOW</v>
@@ -1628,6 +1715,9 @@
         <v/>
       </c>
       <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
         <v/>
       </c>
     </row>
@@ -1635,8 +1725,8 @@
       <c r="A31" t="str">
         <v>SL1029</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>1</v>
       </c>
       <c r="C31" t="str">
         <v>Bantam ARMAJOINT 190 CUSTOM PARTS</v>
@@ -1669,6 +1759,9 @@
         <v/>
       </c>
       <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
         <v/>
       </c>
     </row>
@@ -1676,8 +1769,8 @@
       <c r="A32" t="str">
         <v>SL1030</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
+      <c r="B32">
+        <v>1</v>
       </c>
       <c r="C32" t="str">
         <v>Bantam BT BAIT 99 CUSTOM PARTS</v>
@@ -1710,6 +1803,9 @@
         <v/>
       </c>
       <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
         <v/>
       </c>
     </row>
@@ -1717,8 +1813,8 @@
       <c r="A33" t="str">
         <v>SL1031</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>Bantam BT BAIT 77 CUSTOM PARTS</v>
@@ -1751,6 +1847,9 @@
         <v/>
       </c>
       <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
         <v/>
       </c>
     </row>
@@ -1758,8 +1857,8 @@
       <c r="A34" t="str">
         <v>SL1032</v>
       </c>
-      <c r="B34" t="str">
-        <v/>
+      <c r="B34">
+        <v>1</v>
       </c>
       <c r="C34" t="str">
         <v>CARDIFF REFRAIN 45XS BOTTOM SPEC</v>
@@ -1792,6 +1891,9 @@
         <v/>
       </c>
       <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
         <v/>
       </c>
     </row>
@@ -1799,8 +1901,8 @@
       <c r="A35" t="str">
         <v>SL1033</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>1</v>
       </c>
       <c r="C35" t="str">
         <v>CARDIFF REFRAIN 50HS</v>
@@ -1833,6 +1935,9 @@
         <v/>
       </c>
       <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
         <v/>
       </c>
     </row>
@@ -1840,8 +1945,8 @@
       <c r="A36" t="str">
         <v>SL1034</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
+      <c r="B36">
+        <v>1</v>
       </c>
       <c r="C36" t="str">
         <v>CARDIFF WINDLIP 85S JET BOOST</v>
@@ -1874,6 +1979,9 @@
         <v/>
       </c>
       <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
         <v/>
       </c>
     </row>
@@ -1881,8 +1989,8 @@
       <c r="A37" t="str">
         <v>SL1035</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>1</v>
       </c>
       <c r="C37" t="str">
         <v>CARDIFF FLUGEL 99F DR FLASH BOOST</v>
@@ -1915,6 +2023,9 @@
         <v/>
       </c>
       <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
         <v/>
       </c>
     </row>
@@ -1922,8 +2033,8 @@
       <c r="A38" t="str">
         <v>SL1036</v>
       </c>
-      <c r="B38" t="str">
-        <v/>
+      <c r="B38">
+        <v>1</v>
       </c>
       <c r="C38" t="str">
         <v>CARDIFF WIND LIP 95S/105S JET BOOST</v>
@@ -1956,6 +2067,9 @@
         <v/>
       </c>
       <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
         <v/>
       </c>
     </row>
@@ -1963,8 +2077,8 @@
       <c r="A39" t="str">
         <v>SL1037</v>
       </c>
-      <c r="B39" t="str">
-        <v/>
+      <c r="B39">
+        <v>1</v>
       </c>
       <c r="C39" t="str">
         <v>CARDIFF WINDLIP STICK 90S JET BOOST</v>
@@ -1997,6 +2111,9 @@
         <v/>
       </c>
       <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v/>
       </c>
     </row>
@@ -2004,8 +2121,8 @@
       <c r="A40" t="str">
         <v>SL1038</v>
       </c>
-      <c r="B40" t="str">
-        <v/>
+      <c r="B40">
+        <v>1</v>
       </c>
       <c r="C40" t="str">
         <v>CARDIFF REFRAIN 42S</v>
@@ -2038,6 +2155,9 @@
         <v/>
       </c>
       <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
         <v/>
       </c>
     </row>
@@ -2045,8 +2165,8 @@
       <c r="A41" t="str">
         <v>SL1039</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>CARDIFF ML BULLET 93F JET BOOST</v>
@@ -2079,6 +2199,9 @@
         <v/>
       </c>
       <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
         <v/>
       </c>
     </row>
@@ -2086,8 +2209,8 @@
       <c r="A42" t="str">
         <v>SL1040</v>
       </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="B42">
+        <v>1</v>
       </c>
       <c r="C42" t="str">
         <v>CARDIFF OOTORO 45F</v>
@@ -2120,6 +2243,9 @@
         <v/>
       </c>
       <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
         <v/>
       </c>
     </row>
@@ -2127,8 +2253,8 @@
       <c r="A43" t="str">
         <v>SL1041</v>
       </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="B43">
+        <v>1</v>
       </c>
       <c r="C43" t="str">
         <v>CARDIFF DIVERISE 55F</v>
@@ -2161,6 +2287,9 @@
         <v/>
       </c>
       <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
         <v/>
       </c>
     </row>
@@ -2168,8 +2297,8 @@
       <c r="A44" t="str">
         <v>SL1042</v>
       </c>
-      <c r="B44" t="str">
-        <v/>
+      <c r="B44">
+        <v>1</v>
       </c>
       <c r="C44" t="str">
         <v>CARDIFF SLASH RUSH 55SS</v>
@@ -2202,6 +2331,9 @@
         <v/>
       </c>
       <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
         <v/>
       </c>
     </row>
@@ -2209,8 +2341,8 @@
       <c r="A45" t="str">
         <v>SL1043</v>
       </c>
-      <c r="B45" t="str">
-        <v/>
+      <c r="B45">
+        <v>1</v>
       </c>
       <c r="C45" t="str">
         <v>CARDIFF FUWATORO</v>
@@ -2243,6 +2375,9 @@
         <v/>
       </c>
       <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
         <v/>
       </c>
     </row>
@@ -2250,8 +2385,8 @@
       <c r="A46" t="str">
         <v>SL1044</v>
       </c>
-      <c r="B46" t="str">
-        <v/>
+      <c r="B46">
+        <v>1</v>
       </c>
       <c r="C46" t="str">
         <v>CARDIFF FUWATORO TOP 35F</v>
@@ -2284,6 +2419,9 @@
         <v/>
       </c>
       <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
         <v/>
       </c>
     </row>
@@ -2291,8 +2429,8 @@
       <c r="A47" t="str">
         <v>SL1045</v>
       </c>
-      <c r="B47" t="str">
-        <v/>
+      <c r="B47">
+        <v>1</v>
       </c>
       <c r="C47" t="str">
         <v>CARDIFF SOKOTORO 30S</v>
@@ -2325,6 +2463,9 @@
         <v/>
       </c>
       <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v/>
       </c>
     </row>
@@ -2332,8 +2473,8 @@
       <c r="A48" t="str">
         <v>SL1046</v>
       </c>
-      <c r="B48" t="str">
-        <v/>
+      <c r="B48">
+        <v>1</v>
       </c>
       <c r="C48" t="str">
         <v>CARDIFF CHIBITORO 25F</v>
@@ -2366,6 +2507,9 @@
         <v/>
       </c>
       <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
         <v/>
       </c>
     </row>
@@ -2373,8 +2517,8 @@
       <c r="A49" t="str">
         <v>SL1047</v>
       </c>
-      <c r="B49" t="str">
-        <v/>
+      <c r="B49">
+        <v>1</v>
       </c>
       <c r="C49" t="str">
         <v>CARDIFF CHIBITORO 25S</v>
@@ -2407,6 +2551,9 @@
         <v/>
       </c>
       <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
         <v/>
       </c>
     </row>
@@ -2414,8 +2561,8 @@
       <c r="A50" t="str">
         <v>SL1048</v>
       </c>
-      <c r="B50" t="str">
-        <v/>
+      <c r="B50">
+        <v>1</v>
       </c>
       <c r="C50" t="str">
         <v>CARDIFF SLIM SWIMMER PREMIUM FINISH</v>
@@ -2448,6 +2595,9 @@
         <v/>
       </c>
       <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
         <v/>
       </c>
     </row>
@@ -2455,8 +2605,8 @@
       <c r="A51" t="str">
         <v>SL1049</v>
       </c>
-      <c r="B51" t="str">
-        <v/>
+      <c r="B51">
+        <v>1</v>
       </c>
       <c r="C51" t="str">
         <v>CARDIFF ROLL SWIMMER PREMIUM FINISH</v>
@@ -2489,6 +2639,9 @@
         <v/>
       </c>
       <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v/>
       </c>
     </row>
@@ -2496,8 +2649,8 @@
       <c r="A52" t="str">
         <v>SL1050</v>
       </c>
-      <c r="B52" t="str">
-        <v/>
+      <c r="B52">
+        <v>1</v>
       </c>
       <c r="C52" t="str">
         <v>CARDIFF SEARCH SWIMMER CAMO EDITION</v>
@@ -2530,6 +2683,9 @@
         <v/>
       </c>
       <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v/>
       </c>
     </row>
@@ -2537,8 +2693,8 @@
       <c r="A53" t="str">
         <v>SL1051</v>
       </c>
-      <c r="B53" t="str">
-        <v/>
+      <c r="B53">
+        <v>1</v>
       </c>
       <c r="C53" t="str">
         <v>CARDIFF SLIM SWIMMER 5.0g</v>
@@ -2571,6 +2727,9 @@
         <v/>
       </c>
       <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v/>
       </c>
     </row>
@@ -2578,8 +2737,8 @@
       <c r="A54" t="str">
         <v>SL1052</v>
       </c>
-      <c r="B54" t="str">
-        <v/>
+      <c r="B54">
+        <v>1</v>
       </c>
       <c r="C54" t="str">
         <v>CARDIFF ROLL SWIMMER 5.0g</v>
@@ -2612,6 +2771,9 @@
         <v/>
       </c>
       <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v/>
       </c>
     </row>
@@ -2619,8 +2781,8 @@
       <c r="A55" t="str">
         <v>SL1053</v>
       </c>
-      <c r="B55" t="str">
-        <v/>
+      <c r="B55">
+        <v>1</v>
       </c>
       <c r="C55" t="str">
         <v>CARDIFF SLIM SWIMMER CAMO EDITION</v>
@@ -2653,6 +2815,9 @@
         <v/>
       </c>
       <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
         <v/>
       </c>
     </row>
@@ -2660,8 +2825,8 @@
       <c r="A56" t="str">
         <v>SL1054</v>
       </c>
-      <c r="B56" t="str">
-        <v/>
+      <c r="B56">
+        <v>1</v>
       </c>
       <c r="C56" t="str">
         <v>CARDIFF ROLL SWIMMER CAMO EDITION</v>
@@ -2694,6 +2859,9 @@
         <v/>
       </c>
       <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
         <v/>
       </c>
     </row>
@@ -2701,8 +2869,8 @@
       <c r="A57" t="str">
         <v>SL1055</v>
       </c>
-      <c r="B57" t="str">
-        <v/>
+      <c r="B57">
+        <v>1</v>
       </c>
       <c r="C57" t="str">
         <v>CARDIFF ROLL SWIMMER 0.9g~3.5g</v>
@@ -2735,6 +2903,9 @@
         <v/>
       </c>
       <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
         <v/>
       </c>
     </row>
@@ -2742,8 +2913,8 @@
       <c r="A58" t="str">
         <v>SL1056</v>
       </c>
-      <c r="B58" t="str">
-        <v/>
+      <c r="B58">
+        <v>1</v>
       </c>
       <c r="C58" t="str">
         <v>CARDIFF SLIM SWIMMER 1.5g~3.5g</v>
@@ -2776,6 +2947,9 @@
         <v/>
       </c>
       <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
         <v/>
       </c>
     </row>
@@ -2783,8 +2957,8 @@
       <c r="A59" t="str">
         <v>SL1057</v>
       </c>
-      <c r="B59" t="str">
-        <v/>
+      <c r="B59">
+        <v>1</v>
       </c>
       <c r="C59" t="str">
         <v>CARDIFF SLIM SWIMMER CE CAMO EDITION</v>
@@ -2817,6 +2991,9 @@
         <v/>
       </c>
       <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
         <v/>
       </c>
     </row>
@@ -2824,8 +3001,8 @@
       <c r="A60" t="str">
         <v>SL1058</v>
       </c>
-      <c r="B60" t="str">
-        <v/>
+      <c r="B60">
+        <v>1</v>
       </c>
       <c r="C60" t="str">
         <v>CARDIFF ROLL SWIMMER CE CAMO EDITION</v>
@@ -2858,6 +3035,9 @@
         <v/>
       </c>
       <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
         <v/>
       </c>
     </row>
@@ -2865,8 +3045,8 @@
       <c r="A61" t="str">
         <v>SL1059</v>
       </c>
-      <c r="B61" t="str">
-        <v/>
+      <c r="B61">
+        <v>1</v>
       </c>
       <c r="C61" t="str">
         <v>CARDIFF ALUMI ROLL 2.8g</v>
@@ -2899,6 +3079,9 @@
         <v/>
       </c>
       <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
         <v/>
       </c>
     </row>
@@ -2906,8 +3089,8 @@
       <c r="A62" t="str">
         <v>SL1060</v>
       </c>
-      <c r="B62" t="str">
-        <v/>
+      <c r="B62">
+        <v>1</v>
       </c>
       <c r="C62" t="str">
         <v>CARDIFF ALUMI SLIM 2.6g</v>
@@ -2940,6 +3123,9 @@
         <v/>
       </c>
       <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
         <v/>
       </c>
     </row>
@@ -2947,8 +3133,8 @@
       <c r="A63" t="str">
         <v>SL1061</v>
       </c>
-      <c r="B63" t="str">
-        <v/>
+      <c r="B63">
+        <v>1</v>
       </c>
       <c r="C63" t="str">
         <v>CARDIFF SEARCH SWIMMER</v>
@@ -2981,6 +3167,9 @@
         <v/>
       </c>
       <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v/>
       </c>
     </row>
@@ -2988,8 +3177,8 @@
       <c r="A64" t="str">
         <v>SL1062</v>
       </c>
-      <c r="B64" t="str">
-        <v/>
+      <c r="B64">
+        <v>1</v>
       </c>
       <c r="C64" t="str">
         <v>CARDIFF ROLL SWIMMER CAMO EDITION</v>
@@ -3022,6 +3211,9 @@
         <v/>
       </c>
       <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
         <v/>
       </c>
     </row>
@@ -3029,8 +3221,8 @@
       <c r="A65" t="str">
         <v>SL1063</v>
       </c>
-      <c r="B65" t="str">
-        <v/>
+      <c r="B65">
+        <v>1</v>
       </c>
       <c r="C65" t="str">
         <v>CARDIFF SLIM SWIMMER CE</v>
@@ -3063,6 +3255,9 @@
         <v/>
       </c>
       <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
         <v/>
       </c>
     </row>
@@ -3070,8 +3265,8 @@
       <c r="A66" t="str">
         <v>SL1064</v>
       </c>
-      <c r="B66" t="str">
-        <v/>
+      <c r="B66">
+        <v>1</v>
       </c>
       <c r="C66" t="str">
         <v>CARDIFF WOBBLE SWIMMER</v>
@@ -3106,10 +3301,13 @@
       <c r="M66" t="str">
         <v/>
       </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N66"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4380,7 +4578,7 @@
         <v>SL1003</v>
       </c>
       <c r="C34" t="str">
-        <v>ZR-U66Z 001</v>
+        <v>ZR-U66Z 001 | 001</v>
       </c>
       <c r="D34" t="str">
         <v>5</v>
@@ -4418,7 +4616,7 @@
         <v>SL1003</v>
       </c>
       <c r="C35" t="str">
-        <v>ZR-U66Z 002</v>
+        <v>ZR-U66Z 002 | 002</v>
       </c>
       <c r="D35" t="str">
         <v>5</v>

--- a/GearSage-client/pkgGear/data_raw/shimano_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_lure_import.xlsx
@@ -3314,7 +3314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L545"/>
+  <dimension ref="A1:Q545"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3353,6 +3353,21 @@
       <c r="L1" t="str">
         <v>AdminCode</v>
       </c>
+      <c r="M1" t="str">
+        <v>hook_size</v>
+      </c>
+      <c r="N1" t="str">
+        <v>depth</v>
+      </c>
+      <c r="O1" t="str">
+        <v>action</v>
+      </c>
+      <c r="P1" t="str">
+        <v>subname</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>other.1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -24028,14 +24043,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L545"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q545"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L741"/>
+  <dimension ref="A1:M741"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24074,6 +24089,9 @@
       <c r="L1" t="str">
         <v>AdminCode</v>
       </c>
+      <c r="M1" t="str">
+        <v>hook_size</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -52197,7 +52215,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L741"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M741"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/shimano_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_lure_import.xlsx
@@ -477,7 +477,7 @@
         <v>glide</v>
       </c>
       <c r="K2" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 190SF FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20190SF%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K3" t="str">
-        <v>images/shimano_lures/FACER 85+SF_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/FACER%2085%2BSF_main.jpg</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -565,7 +565,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K4" t="str">
-        <v>images/shimano_lures/MD ZUMVERNO 95SP_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/MD%20ZUMVERNO%2095SP_main.jpg</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -609,7 +609,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K5" t="str">
-        <v>images/shimano_lures/LIGEN 66F WALKING SPEC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/LIGEN%2066F%20WALKING%20SPEC_main.jpg</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -653,7 +653,7 @@
         <v>glide</v>
       </c>
       <c r="K6" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 280SF ARMABOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20280SF%20ARMABOOST_main.jpg</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -697,7 +697,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K7" t="str">
-        <v>images/shimano_lures/GRAVITATOR 220SF ARMABOOST_FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/GRAVITATOR%20220SF%20ARMABOOST_FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -741,7 +741,7 @@
         <v>glide</v>
       </c>
       <c r="K8" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 190F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20190F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -785,7 +785,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K9" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 77F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2077F_main.jpg</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -829,7 +829,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K10" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 99SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2099SS_main.jpg</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -873,7 +873,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K11" t="str">
-        <v>images/shimano_lures/SCORPION WORLD JERK 110F_110S FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/SCORPION%20WORLD%20JERK%20110F_110S%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -917,7 +917,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K12" t="str">
-        <v>images/shimano_lures/SCORPION WORLD JERK 115F_115S FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/SCORPION%20WORLD%20JERK%20115F_115S%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -961,7 +961,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K13" t="str">
-        <v>images/shimano_lures/Bantam WORLD MINNOW 115SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20MINNOW%20115SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1005,7 +1005,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K14" t="str">
-        <v>images/shimano_lures/Bantam WORLD MINNOW 115F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20MINNOW%20115F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1049,7 +1049,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K15" t="str">
-        <v>images/shimano_lures/Bantam WORLD CRANK 73F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20CRANK%2073F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1093,7 +1093,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K16" t="str">
-        <v>images/shimano_lures/Bantam ZUMVERNO 95SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ZUMVERNO%2095SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1137,7 +1137,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K17" t="str">
-        <v>images/shimano_lures/Bantam WORLD POP 69F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20POP%2069F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1181,7 +1181,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K18" t="str">
-        <v>images/shimano_lures/SCORPION JERK 90S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/SCORPION%20JERK%2090S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1225,7 +1225,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K19" t="str">
-        <v>images/shimano_lures/Bantam WORLD RUSH 56F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20WORLD%20RUSH%2056F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1269,7 +1269,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K20" t="str">
-        <v>images/shimano_lures/Bantam UNDURATOR 88F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20UNDURATOR%2088F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K21" t="str">
-        <v>images/shimano_lures/Bantam OLIVA CRANK FLAT 65F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20OLIVA%20CRANK%20FLAT%2065F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K22" t="str">
-        <v>images/shimano_lures/Bantam ENBER 60SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ENBER%2060SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1401,7 +1401,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K23" t="str">
-        <v>images/shimano_lures/Bantam LIGEN 66F FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20LIGEN%2066F%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1445,7 +1445,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K24" t="str">
-        <v>images/shimano_lures/Bantam MD ZUMVERNO 115SP_115SP FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20MD%20ZUMVERNO%20115SP_115SP%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1489,7 +1489,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K25" t="str">
-        <v>images/shimano_lures/Bantam SWAGY MDW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20SWAGY%20MDW_main.jpg</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1533,7 +1533,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K26" t="str">
-        <v>images/shimano_lures/Bantam SWAGY TW_DW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20SWAGY%20TW_DW_main.jpg</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1577,7 +1577,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K27" t="str">
-        <v>images/shimano_lures/Bantam JIJIL 70_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20JIJIL%2070_main.jpg</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1621,7 +1621,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K28" t="str">
-        <v>images/shimano_lures/Bantam MACBETH 50 RATTLE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20MACBETH%2050%20RATTLE_main.jpg</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1665,7 +1665,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K29" t="str">
-        <v>images/shimano_lures/Bantam JIJIL PROP 67SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20JIJIL%20PROP%2067SS_main.jpg</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1709,7 +1709,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K30" t="str">
-        <v>images/shimano_lures/Bantam MACBETH SHALLOW_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20MACBETH%20SHALLOW_main.jpg</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1753,7 +1753,7 @@
         <v>glide</v>
       </c>
       <c r="K31" t="str">
-        <v>images/shimano_lures/Bantam ARMAJOINT 190 CUSTOM PARTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20ARMAJOINT%20190%20CUSTOM%20PARTS_main.jpg</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1797,7 +1797,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K32" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 99 CUSTOM PARTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2099%20CUSTOM%20PARTS_main.jpg</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1841,7 +1841,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K33" t="str">
-        <v>images/shimano_lures/Bantam BT BAIT 77 CUSTOM PARTS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/Bantam%20BT%20BAIT%2077%20CUSTOM%20PARTS_main.jpg</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1885,7 +1885,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K34" t="str">
-        <v>images/shimano_lures/CARDIFF REFRAIN 45XS BOTTOM SPEC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20REFRAIN%2045XS%20BOTTOM%20SPEC_main.jpg</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1929,7 +1929,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K35" t="str">
-        <v>images/shimano_lures/CARDIFF REFRAIN 50HS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20REFRAIN%2050HS_main.jpg</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -1973,7 +1973,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K36" t="str">
-        <v>images/shimano_lures/CARDIFF WINDLIP 85S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WINDLIP%2085S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2017,7 +2017,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K37" t="str">
-        <v>images/shimano_lures/CARDIFF FLUGEL 99F DR FLASH BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20FLUGEL%2099F%20DR%20FLASH%20BOOST_main.jpg</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2061,7 +2061,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K38" t="str">
-        <v>images/shimano_lures/CARDIFF WIND LIP 95S_105S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WIND%20LIP%2095S_105S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2105,7 +2105,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K39" t="str">
-        <v>images/shimano_lures/CARDIFF WINDLIP STICK 90S JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WINDLIP%20STICK%2090S%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K40" t="str">
-        <v>images/shimano_lures/CARDIFF REFRAIN 42S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20REFRAIN%2042S_main.jpg</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K41" t="str">
-        <v>images/shimano_lures/CARDIFF ML BULLET 93F JET BOOST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ML%20BULLET%2093F%20JET%20BOOST_main.jpg</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2237,7 +2237,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K42" t="str">
-        <v>images/shimano_lures/CARDIFF OOTORO 45F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20OOTORO%2045F_main.jpg</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2281,7 +2281,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K43" t="str">
-        <v>images/shimano_lures/CARDIFF DIVERISE 55F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20DIVERISE%2055F_main.jpg</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2325,7 +2325,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K44" t="str">
-        <v>images/shimano_lures/CARDIFF SLASH RUSH 55SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLASH%20RUSH%2055SS_main.jpg</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2369,7 +2369,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K45" t="str">
-        <v>images/shimano_lures/CARDIFF FUWATORO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20FUWATORO%20TOP%2035F_main.jpg</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2413,7 +2413,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K46" t="str">
-        <v>images/shimano_lures/CARDIFF FUWATORO TOP 35F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20FUWATORO%20TOP%2035F_main.jpg</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2457,7 +2457,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K47" t="str">
-        <v>images/shimano_lures/CARDIFF SOKOTORO 30S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SOKOTORO%2030S_main.jpg</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2501,7 +2501,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K48" t="str">
-        <v>images/shimano_lures/CARDIFF CHIBITORO 25F_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20CHIBITORO%2025F_main.jpg</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2545,7 +2545,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K49" t="str">
-        <v>images/shimano_lures/CARDIFF CHIBITORO 25S_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20CHIBITORO%2025S_main.jpg</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2589,7 +2589,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K50" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER PREMIUM FINISH_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20PREMIUM%20FINISH_main.jpg</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2633,7 +2633,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K51" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER PREMIUM FINISH_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20PREMIUM%20FINISH_main.jpg</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2677,7 +2677,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K52" t="str">
-        <v>images/shimano_lures/CARDIFF SEARCH SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SEARCH%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2721,7 +2721,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K53" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER 5.0g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%205.0g_main.jpg</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2765,7 +2765,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K54" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER 5.0g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%205.0g_main.jpg</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2809,7 +2809,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K55" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2853,7 +2853,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K56" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -2897,7 +2897,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K57" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER 0.9g~3.5g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%200.9g~3.5g_main.jpg</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -2941,7 +2941,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K58" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER 1.5g~3.5g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%201.5g~3.5g_main.jpg</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K59" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER CE CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20CE%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K60" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER CE CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20CE%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3073,7 +3073,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K61" t="str">
-        <v>images/shimano_lures/CARDIFF ALUMI ROLL 2.8g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ALUMI%20ROLL%202.8g_main.jpg</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3117,7 +3117,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K62" t="str">
-        <v>images/shimano_lures/CARDIFF ALUMI SLIM 2.6g_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ALUMI%20SLIM%202.6g_main.jpg</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3161,7 +3161,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K63" t="str">
-        <v>images/shimano_lures/CARDIFF SEARCH SWIMMER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SEARCH%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3205,7 +3205,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K64" t="str">
-        <v>images/shimano_lures/CARDIFF ROLL SWIMMER CAMO EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20ROLL%20SWIMMER%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3249,7 +3249,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K65" t="str">
-        <v>images/shimano_lures/CARDIFF SLIM SWIMMER CE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20SLIM%20SWIMMER%20CE%20CAMO%20EDITION_main.jpg</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3293,7 +3293,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K66" t="str">
-        <v>images/shimano_lures/CARDIFF WOBBLE SWIMMER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lures/CARDIFF%20WOBBLE%20SWIMMER_main.jpg</v>
       </c>
       <c r="L66" t="str">
         <v/>
